--- a/output/pdf_financials_xlsx/AEMC.xlsx
+++ b/output/pdf_financials_xlsx/AEMC.xlsx
@@ -1040,13 +1040,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004304</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00091</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001991</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1978,13 +1978,13 @@
         <v>-1.254772</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.003016</v>
+        <v>-1.998712</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.259091</v>
+        <v>-2.260001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.33865</v>
+        <v>-2.340641</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.988321</v>
@@ -2094,13 +2094,13 @@
         <v>-1.253286</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.000498</v>
+        <v>-1.996194</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.227795</v>
+        <v>-2.228705</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.206408</v>
+        <v>-2.208399</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.861768</v>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-319.68955115934</v>
+        <v>-319.8201365550138</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-173.006151324946</v>
+        <v>-173.1622671690183</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-338.3348367715369</v>
@@ -2382,19 +2382,19 @@
         <v>0.494145</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.797573</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.395742</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.939327</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.284445</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.687785</v>
       </c>
     </row>
     <row r="35">
@@ -2498,19 +2498,19 @@
         <v>0.494145</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.797573</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.395742</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.939327</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.284445</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.687785</v>
       </c>
     </row>
     <row r="37">
@@ -3194,19 +3194,19 @@
         <v>0.720934</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.286882</v>
+        <v>1.489309</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.244514</v>
+        <v>1.848772</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.076932</v>
+        <v>1.137605</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.497113</v>
+        <v>0.212668</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.749786</v>
+        <v>0.062001</v>
       </c>
     </row>
     <row r="49">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -48087,11 +48087,7 @@
           <t>General and administrative expense total</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -59659,7 +59655,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">

--- a/output/pdf_financials_xlsx/AEMC.xlsx
+++ b/output/pdf_financials_xlsx/AEMC.xlsx
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.08516899999999999</v>
+        <v>0.323502</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.109438</v>
+        <v>0.350227</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.348958</v>
+        <v>0.657341</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.675721</v>
+        <v>1.304147</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.321226</v>
+        <v>0.559559</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.349326</v>
+        <v>0.5901149999999999</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.422601</v>
+        <v>1.730984</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.149008</v>
+        <v>1.777434</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.522775</v>
@@ -1128,13 +1128,13 @@
         <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.025979</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.011775</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.004909</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>-0.00895</v>
@@ -1244,22 +1244,22 @@
         <v>-0.013738</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.001734</v>
+        <v>0.197404</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>-0.006385</v>
+        <v>0.071232</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.014085</v>
+        <v>0.083847</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.164048</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0.02146</v>
+        <v>0.068565</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-0.016019</v>
+        <v>0.512223</v>
       </c>
     </row>
     <row r="16">
@@ -1314,7 +1314,7 @@
         <v>-9.788449</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-8.841214000000001</v>
+        <v>-9.060214</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>-3.683854</v>
@@ -1336,7 +1336,7 @@
         <v>-0.398565</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.566747</v>
+        <v>0.103863</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.039514</v>
@@ -1372,7 +1372,7 @@
         <v>-0</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>0.219</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>-0</v>
@@ -2008,19 +2008,19 @@
         <v>-4.338539</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.32892</v>
+        <v>-4.302941</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.138041</v>
+        <v>-2.126266</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.703013</v>
+        <v>-1.698104</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-9.779498999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-8.835523999999999</v>
+        <v>-9.054524000000001</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-3.683854</v>
@@ -2124,19 +2124,19 @@
         <v>-4.305674</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.323561</v>
+        <v>-4.297582</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.136985</v>
+        <v>-2.12521</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.703013</v>
+        <v>-1.698104</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-9.779498999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-8.835523999999999</v>
+        <v>-9.054524000000001</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-3.683854</v>
@@ -2186,13 +2186,13 @@
         <v>-75.76519668240857</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-382.5401867240476</v>
+        <v>-380.2416158212885</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-367.1549500978456</v>
+        <v>-365.1318897874541</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-750.1367678734248</v>
+        <v>-747.9744699969607</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-141958.1797067789</v>
@@ -2224,7 +2224,7 @@
         <v>-17.64271558781829</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-24.2339383832553</v>
+        <v>-4.44115194663588</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-1.322280973161853</v>
@@ -2260,7 +2260,7 @@
         <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.417161448945908</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>-0</v>
@@ -2410,43 +2410,43 @@
         <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>0.66857</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>0.429031</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>0.227331</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>0.068199</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>0.057389</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>0.060322</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>0.086174</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>3.184206</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0</v>
+        <v>1.510341</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>0.713639</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>1.258768</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0</v>
+        <v>1.750029</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>0.439844</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
@@ -2468,43 +2468,43 @@
         <v>1.07645</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.07645</v>
+        <v>1.74502</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.134757</v>
+        <v>2.563788</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3.945929</v>
+        <v>4.17326</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.613607</v>
+        <v>1.681806</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3.778151</v>
+        <v>3.83554</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.577421</v>
+        <v>1.637743</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.419693</v>
+        <v>2.505867</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.760727</v>
+        <v>4.944933</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.779166</v>
+        <v>2.289507</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.494145</v>
+        <v>1.207784</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.797573</v>
+        <v>2.056341</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.395742</v>
+        <v>2.145771</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>3.939327</v>
+        <v>4.379171</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>1.284445</v>
@@ -3164,43 +3164,43 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.635594</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.559036</v>
+        <v>2.130005</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.00439</v>
+        <v>0.7770590000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.272888</v>
+        <v>0.204689</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.595158</v>
+        <v>0.5377690000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.563993</v>
+        <v>0.503671</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.334687</v>
+        <v>0.248513</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.3873</v>
+        <v>0.203094</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.630917</v>
+        <v>0.120576</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.720934</v>
+        <v>0.007295</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.489309</v>
+        <v>0.230541</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.848772</v>
+        <v>0.098743</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.137605</v>
+        <v>0.697761</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.212668</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.008513</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.01268</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -3803,19 +3803,19 @@
         <v>3.966897</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>3.92859</v>
+        <v>4.244482</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>3.543445</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>3.367375</v>
+        <v>3.576805</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4.249505</v>
+        <v>4.313046</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>3.85542</v>
+        <v>3.932671</v>
       </c>
       <c r="P58" s="3" t="n">
         <v>17.41727</v>
@@ -3977,19 +3977,19 @@
         <v>0.047</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.364195</v>
+        <v>0.048303</v>
       </c>
       <c r="L61" s="3" t="n">
         <v>0.048417</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.210779</v>
+        <v>0.001349</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.063541</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.077251</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>0</v>
@@ -4248,25 +4248,25 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.010232</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.001825</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>0.001825</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0</v>
+        <v>0.043004</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0</v>
+        <v>0.01421</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0</v>
+        <v>0.098162</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>0</v>
@@ -4275,28 +4275,28 @@
         <v>0</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0</v>
+        <v>0.027182</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0</v>
+        <v>0.034276</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0</v>
+        <v>0.055495</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0</v>
+        <v>0.129218</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0</v>
+        <v>0.027667</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0</v>
+        <v>0.124438</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0</v>
+        <v>0.163348</v>
       </c>
     </row>
     <row r="67">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P69" s="3" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
         <v>0.134462</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.787005</v>
+        <v>0.287005</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0.303737</v>
@@ -5124,10 +5124,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O80" s="3" t="n">
+        <v>0.09567548711739134</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -5292,13 +5290,13 @@
         <v>0.060987</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0</v>
+        <v>0.049332</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0</v>
+        <v>0.048347</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="M83" s="3" t="n">
         <v>0</v>
@@ -5350,13 +5348,13 @@
         <v>0.060987</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0</v>
+        <v>0.049332</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0</v>
+        <v>0.048347</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="M84" s="3" t="n">
         <v>0</v>
@@ -5408,13 +5406,13 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.162959</v>
+        <v>0.113627</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.095347</v>
+        <v>0.047</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0.079</v>
+        <v>0.047</v>
       </c>
       <c r="M85" s="3" t="n">
         <v>0.14247</v>
@@ -5566,55 +5564,55 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>10.922792</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>13.981072</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>13.981072</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>22.599946</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>24.769518</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>25.247857</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>30.241769</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>32.265528</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>36.710359</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>38.672646</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>39.662935</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>41.798903</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>47.069153</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>47.274153</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>70.210161</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>80.04269499999999</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>0</v>
+        <v>83.51175000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5798,13 +5796,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.815226</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.146633</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.184901</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -7277,22 +7275,22 @@
         <v>3.958903</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-0.765814</v>
+        <v>0.337019</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>-1.365849</v>
+        <v>0.08047799999999999</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>-1.061879</v>
+        <v>-0.915694</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>-0.771296</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>-4.922112</v>
+        <v>-4.345665</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>-2.747379</v>
+        <v>-1.576701</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>0.00792</v>
@@ -7909,22 +7907,22 @@
         <v>-0.003161</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-0.263112</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0</v>
+        <v>-0.042855</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>0</v>
+        <v>-0.159376</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0</v>
+        <v>-0.058725</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>0</v>
+        <v>-0.06252199999999999</v>
       </c>
       <c r="N128" s="3" t="n">
         <v>-0.213335</v>
@@ -9235,7 +9233,11 @@
           <t>Due to related parties – Note 8</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -9835,7 +9837,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10601,7 +10607,11 @@
           <t>Marketable securities – Note 5</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11003,7 +11013,11 @@
           <t>Due to related parties – Note 10</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11403,7 +11417,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11898,7 +11916,11 @@
           <t>Right of use asset – Note 8</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12193,7 +12215,11 @@
           <t>Due to related parties – Note 12</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -12290,7 +12316,11 @@
           <t>Loan payable – Note 9</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12793,7 +12823,11 @@
           <t>Share capital – Note 10</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13676,7 +13710,11 @@
           <t>Security deposit and restricted cash - Note 5</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13763,7 +13801,11 @@
           <t>Marketable securities - Note 6</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14032,7 +14074,11 @@
           <t>Right of use asset - Note 10</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -14400,7 +14446,11 @@
           <t>Income tax payable - Note 17</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14689,7 +14739,11 @@
           <t>Due to related parties - Note 15</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15079,7 +15133,11 @@
           <t>Deferred tax liability - Note 17</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -15368,7 +15426,11 @@
           <t>Share capital - Note 12 $</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16134,7 +16196,11 @@
           <t>Property, plant and equipment - Note 7 &amp; 10</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16233,7 +16299,11 @@
           <t>Income tax payable - Note 18</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -16425,7 +16495,11 @@
           <t>Due to related parties - Note 14</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -16617,7 +16691,11 @@
           <t>Deferred tax liability - Note 18</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -16712,7 +16790,11 @@
           <t>Share capital - Note 11 $</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -17072,7 +17154,11 @@
           <t>Due to related parties - Note 10</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -17771,7 +17857,11 @@
           <t>Due to related parties - Note 13</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -18072,7 +18162,11 @@
           <t>Share capital - Note 10 $</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -18557,7 +18651,11 @@
           <t>Security deposit and restricted cash - Note 6</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -18656,7 +18754,11 @@
           <t>Marketable securities - Note 7</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -19755,7 +19857,11 @@
           <t>Due from related parties - Note 14</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -19856,7 +19962,11 @@
           <t>Income tax payable - Note 19</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -20258,7 +20368,11 @@
           <t>Security deposit and restricted cash - Note 5 2,000,973</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -20357,7 +20471,11 @@
           <t>Marketable securities - Note 6 429,031</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -20664,7 +20782,11 @@
           <t>Due from related parties - Note 14 10,266</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -21480,7 +21602,11 @@
           <t>Income tax payable - Note 18 103,863</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -21785,7 +21911,11 @@
           <t>Due to related parties - Note 14 32,738</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22302,7 +22432,11 @@
           <t>Share capital - Note 11 $ 22,599,946 $</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -23304,7 +23438,11 @@
           <t>Security deposit and restricted cash - Note 13</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -23403,7 +23541,11 @@
           <t>Marketable securities - Note 4</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -23605,7 +23747,11 @@
           <t>Due from related parties - Note 11</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -24401,7 +24547,11 @@
           <t>Due to related parties - Note 11</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -24502,7 +24652,11 @@
           <t>Share capital - Note 8</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -24601,7 +24755,11 @@
           <t>Contributed Surplus - Note 8</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -25199,7 +25357,11 @@
           <t>Due from related parties - Note 9</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="n">
         <v>0.010232</v>
       </c>
@@ -25397,7 +25559,11 @@
           <t>Equipment - Note 5</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="n">
         <v>0.008513</v>
       </c>
@@ -25595,7 +25761,11 @@
           <t>Share capital - Note 7</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="n">
         <v>10.922792</v>
       </c>
@@ -25795,7 +25965,11 @@
           <t>Contributed Surplus - Note 7</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="n">
         <v>0.815226</v>
       </c>
@@ -33724,7 +33898,11 @@
           <t>Impairment/ Write-off of exploration and evaluation assets - Note 8</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -35743,7 +35921,11 @@
           <t>Share issuance costs - Note 12</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -37309,7 +37491,11 @@
           <t>Share issuance costs - Note 11</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -38079,7 +38265,11 @@
           <t>Write-off of exploration and evaluation assets - Note 8</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -39548,7 +39738,11 @@
           <t>Share issuance costs - Note 10</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -46472,7 +46666,11 @@
           <t>Other income – Note 5</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -46769,7 +46967,11 @@
           <t>Deferred income tax expense – Note 11</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -48556,7 +48758,11 @@
           <t>Deferred income tax expense – Note 16</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -49148,7 +49354,11 @@
           <t>Interest expense of lease liability – Note 8</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -49942,7 +50152,11 @@
           <t>Other income – Note 6</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -51629,7 +51843,11 @@
           <t>Interest expense of lease liability - Note 10</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -52488,7 +52706,11 @@
           <t>Other income - Note 8</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -57572,7 +57794,11 @@
           <t>Income tax expense - Note 19</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -58572,7 +58798,11 @@
           <t>Consulting - Note 14</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -59552,7 +59782,11 @@
           <t>Income tax expense - Note 18</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
           <t>-</t>
@@ -60354,7 +60588,11 @@
           <t>Consulting - Note 11</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -65144,7 +65382,11 @@
           <t>Consulting - Note 9</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E579" s="5" t="n">
         <v>0.238333</v>
       </c>

--- a/output/pdf_financials_xlsx/AEMC.xlsx
+++ b/output/pdf_financials_xlsx/AEMC.xlsx
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.236057</v>
+        <v>0.303795</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.239888</v>
+        <v>0.306409</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.073643</v>
+        <v>1.101143</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.473287</v>
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.559559</v>
+        <v>0.627297</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.5901149999999999</v>
+        <v>0.656636</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.730984</v>
+        <v>1.758484</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.777434</v>
@@ -1354,13 +1354,13 @@
         <v>-0.302038</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.07922899999999999</v>
+        <v>-0.04265</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.317674</v>
+        <v>-0.019</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.178652</v>
+        <v>-0.032</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -2242,13 +2242,13 @@
         <v>-11.05836471024139</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-17.12396715649511</v>
+        <v>-9.218053985592602</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-7.322142315650498</v>
+        <v>-0.4379354432448343</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-4.126941592822228</v>
+        <v>-0.7392143998965101</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -6851,13 +6851,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004991</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006685</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.125132</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7122,13 +7122,13 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.058663</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.566344</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.352152</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004991</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006685</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.125132</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8313,13 +8313,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.007</v>
+        <v>-0.011991</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.901521</v>
+        <v>-0.908206</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.840298</v>
+        <v>-1.96543</v>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
@@ -26913,7 +26913,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -27526,7 +27530,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -29108,7 +29116,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -36024,7 +36036,11 @@
           <t>Shares issued for cash - Note 12</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -37586,7 +37602,11 @@
           <t>Shares issued for cash - Note 11</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -39841,7 +39861,11 @@
           <t>Shares issued for cash - Note 10</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -41219,7 +41243,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -43611,7 +43639,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E358" s="5" t="n">
         <v>-0.004991</v>
       </c>
@@ -44013,7 +44045,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -45025,7 +45061,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E372" s="5" t="n">
         <v>2.562661</v>
       </c>
@@ -52908,7 +52948,11 @@
           <t>Income tax recovery - Note 17</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -53852,7 +53896,11 @@
           <t>Income tax recovery - Note 18</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -56590,7 +56638,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
           <t>-</t>
@@ -58901,7 +58953,11 @@
           <t>Directors' fees - Note 14</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -60691,7 +60747,11 @@
           <t>Directors' fees - Note 11</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -60988,7 +61048,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E535" s="5" t="n">
         <v>0.06773800000000001</v>
       </c>
@@ -65485,7 +65549,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
